--- a/data/xlsx/lfmeab--supply-chain-management-for-footwear-and-leather-goods-sector.xlsx
+++ b/data/xlsx/lfmeab--supply-chain-management-for-footwear-and-leather-goods-sector.xlsx
@@ -648,7 +648,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -670,7 +672,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -692,7 +696,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -714,7 +720,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -736,7 +744,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -756,7 +766,9 @@
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -782,7 +794,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -808,7 +822,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -830,7 +846,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -852,7 +870,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -874,7 +894,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -896,7 +918,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -918,7 +942,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -940,7 +966,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -962,7 +990,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -984,7 +1014,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -1006,7 +1038,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
